--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,6 +979,434 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122235369</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90750</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>563130</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7040389</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122234448</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78639</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>563179</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7040282</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122235058</v>
+      </c>
+      <c r="B7" t="n">
+        <v>74741</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>563147</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7040405</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122234993</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78639</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>563147</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7040405</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122235369</v>
+        <v>122234993</v>
       </c>
       <c r="B5" t="n">
-        <v>90750</v>
+        <v>78643</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563130</v>
+        <v>563147</v>
       </c>
       <c r="R5" t="n">
-        <v>7040389</v>
+        <v>7040405</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,19 +1054,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122234448</v>
+        <v>122235369</v>
       </c>
       <c r="B6" t="n">
-        <v>78639</v>
+        <v>90757</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563179</v>
+        <v>563130</v>
       </c>
       <c r="R6" t="n">
-        <v>7040282</v>
+        <v>7040389</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1158,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1168,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122235058</v>
+        <v>122234448</v>
       </c>
       <c r="B7" t="n">
-        <v>74741</v>
+        <v>78643</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563147</v>
+        <v>563179</v>
       </c>
       <c r="R7" t="n">
-        <v>7040405</v>
+        <v>7040282</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1278,9 +1268,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234993</v>
+        <v>122235058</v>
       </c>
       <c r="B8" t="n">
-        <v>78639</v>
+        <v>74745</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>122234993</v>
       </c>
       <c r="B5" t="n">
-        <v>78643</v>
+        <v>78645</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122235369</v>
+        <v>122235058</v>
       </c>
       <c r="B6" t="n">
-        <v>90757</v>
+        <v>74747</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563130</v>
+        <v>563147</v>
       </c>
       <c r="R6" t="n">
-        <v>7040389</v>
+        <v>7040405</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,19 +1156,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122234448</v>
+        <v>122235369</v>
       </c>
       <c r="B7" t="n">
-        <v>78643</v>
+        <v>90759</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563179</v>
+        <v>563130</v>
       </c>
       <c r="R7" t="n">
-        <v>7040282</v>
+        <v>7040389</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1260,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1270,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122235058</v>
+        <v>122234448</v>
       </c>
       <c r="B8" t="n">
-        <v>74745</v>
+        <v>78645</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,13 +1337,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563147</v>
+        <v>563179</v>
       </c>
       <c r="R8" t="n">
-        <v>7040405</v>
+        <v>7040282</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,9 +1370,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,12 +1397,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234993</v>
+        <v>122235058</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>74747</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122235058</v>
+        <v>122235369</v>
       </c>
       <c r="B6" t="n">
-        <v>74747</v>
+        <v>90759</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563147</v>
+        <v>563130</v>
       </c>
       <c r="R6" t="n">
-        <v>7040405</v>
+        <v>7040389</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,9 +1156,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122235369</v>
+        <v>122234993</v>
       </c>
       <c r="B7" t="n">
-        <v>90759</v>
+        <v>78645</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563130</v>
+        <v>563147</v>
       </c>
       <c r="R7" t="n">
-        <v>7040389</v>
+        <v>7040405</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,19 +1268,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,12 +1285,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234448</v>
+        <v>122235058</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>74747</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563179</v>
+        <v>563147</v>
       </c>
       <c r="R5" t="n">
-        <v>7040282</v>
+        <v>7040405</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,19 +1054,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122235369</v>
+        <v>122234448</v>
       </c>
       <c r="B6" t="n">
-        <v>90775</v>
+        <v>78645</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563130</v>
+        <v>563179</v>
       </c>
       <c r="R6" t="n">
-        <v>7040389</v>
+        <v>7040282</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1158,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1168,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122235058</v>
+        <v>122235369</v>
       </c>
       <c r="B7" t="n">
-        <v>74747</v>
+        <v>90775</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563147</v>
+        <v>563130</v>
       </c>
       <c r="R7" t="n">
-        <v>7040405</v>
+        <v>7040389</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1278,9 +1268,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,12 +1295,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122235058</v>
+        <v>122235369</v>
       </c>
       <c r="B5" t="n">
-        <v>74747</v>
+        <v>90785</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563147</v>
+        <v>563130</v>
       </c>
       <c r="R5" t="n">
-        <v>7040405</v>
+        <v>7040389</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,9 +1054,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122234448</v>
+        <v>122235058</v>
       </c>
       <c r="B6" t="n">
-        <v>78645</v>
+        <v>74747</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1133,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563179</v>
+        <v>563147</v>
       </c>
       <c r="R6" t="n">
-        <v>7040282</v>
+        <v>7040405</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,19 +1166,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122235369</v>
+        <v>122234993</v>
       </c>
       <c r="B7" t="n">
-        <v>90775</v>
+        <v>78646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563130</v>
+        <v>563147</v>
       </c>
       <c r="R7" t="n">
-        <v>7040389</v>
+        <v>7040405</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1268,19 +1268,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,22 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234993</v>
+        <v>122234448</v>
       </c>
       <c r="B8" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,13 +1337,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563147</v>
+        <v>563179</v>
       </c>
       <c r="R8" t="n">
-        <v>7040405</v>
+        <v>7040282</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,9 +1370,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,12 +1397,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122235369</v>
+        <v>122234448</v>
       </c>
       <c r="B5" t="n">
-        <v>90785</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563130</v>
+        <v>563179</v>
       </c>
       <c r="R5" t="n">
-        <v>7040389</v>
+        <v>7040282</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234448</v>
+        <v>122235369</v>
       </c>
       <c r="B8" t="n">
-        <v>78646</v>
+        <v>90785</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563179</v>
+        <v>563130</v>
       </c>
       <c r="R8" t="n">
-        <v>7040282</v>
+        <v>7040389</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234448</v>
+        <v>122235369</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>90797</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563179</v>
+        <v>563130</v>
       </c>
       <c r="R5" t="n">
-        <v>7040282</v>
+        <v>7040389</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,7 +1096,7 @@
         <v>122235058</v>
       </c>
       <c r="B6" t="n">
-        <v>74747</v>
+        <v>74752</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>122234993</v>
       </c>
       <c r="B7" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122235369</v>
+        <v>122234448</v>
       </c>
       <c r="B8" t="n">
-        <v>90785</v>
+        <v>78651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563130</v>
+        <v>563179</v>
       </c>
       <c r="R8" t="n">
-        <v>7040389</v>
+        <v>7040282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122235369</v>
+        <v>122235058</v>
       </c>
       <c r="B5" t="n">
-        <v>90797</v>
+        <v>74752</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563130</v>
+        <v>563147</v>
       </c>
       <c r="R5" t="n">
-        <v>7040389</v>
+        <v>7040405</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,19 +1054,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122235058</v>
+        <v>122234448</v>
       </c>
       <c r="B6" t="n">
-        <v>74752</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563147</v>
+        <v>563179</v>
       </c>
       <c r="R6" t="n">
-        <v>7040405</v>
+        <v>7040282</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1166,9 +1156,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122234993</v>
+        <v>122235369</v>
       </c>
       <c r="B7" t="n">
-        <v>78651</v>
+        <v>90804</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563147</v>
+        <v>563130</v>
       </c>
       <c r="R7" t="n">
-        <v>7040405</v>
+        <v>7040389</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1268,9 +1268,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,19 +1295,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234448</v>
+        <v>122234993</v>
       </c>
       <c r="B8" t="n">
         <v>78651</v>
@@ -1337,13 +1347,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563179</v>
+        <v>563147</v>
       </c>
       <c r="R8" t="n">
-        <v>7040282</v>
+        <v>7040405</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1370,19 +1380,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,12 +1397,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122235058</v>
+        <v>122234448</v>
       </c>
       <c r="B5" t="n">
-        <v>74752</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563147</v>
+        <v>563179</v>
       </c>
       <c r="R5" t="n">
-        <v>7040405</v>
+        <v>7040282</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,9 +1054,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122234448</v>
+        <v>122235058</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>74752</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1133,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563179</v>
+        <v>563147</v>
       </c>
       <c r="R6" t="n">
-        <v>7040282</v>
+        <v>7040405</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,19 +1166,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,12 +1183,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>122234448</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,11 +998,6 @@
       </c>
       <c r="E5" t="n">
         <v>6425</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122235058</v>
+        <v>122234993</v>
       </c>
       <c r="B6" t="n">
-        <v>74752</v>
+        <v>78652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,7 +1188,7 @@
         <v>122235369</v>
       </c>
       <c r="B7" t="n">
-        <v>90804</v>
+        <v>90809</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,11 +1202,6 @@
       </c>
       <c r="E7" t="n">
         <v>1108</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1307,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234993</v>
+        <v>122235058</v>
       </c>
       <c r="B8" t="n">
-        <v>78651</v>
+        <v>74753</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1308,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6440</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234448</v>
+        <v>122235369</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>90822</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,16 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563179</v>
+        <v>563130</v>
       </c>
       <c r="R5" t="n">
-        <v>7040282</v>
+        <v>7040389</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1061,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122234993</v>
+        <v>122235058</v>
       </c>
       <c r="B6" t="n">
-        <v>78652</v>
+        <v>74757</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,16 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122235369</v>
+        <v>122234448</v>
       </c>
       <c r="B7" t="n">
-        <v>90809</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,16 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563130</v>
+        <v>563179</v>
       </c>
       <c r="R7" t="n">
-        <v>7040389</v>
+        <v>7040282</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1265,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122235058</v>
+        <v>122234993</v>
       </c>
       <c r="B8" t="n">
-        <v>74753</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,16 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122235369</v>
+        <v>122234448</v>
       </c>
       <c r="B5" t="n">
-        <v>90822</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563130</v>
+        <v>563179</v>
       </c>
       <c r="R5" t="n">
-        <v>7040389</v>
+        <v>7040282</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122235058</v>
+        <v>122235369</v>
       </c>
       <c r="B6" t="n">
-        <v>74757</v>
+        <v>90835</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,13 +1133,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563147</v>
+        <v>563130</v>
       </c>
       <c r="R6" t="n">
-        <v>7040405</v>
+        <v>7040389</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1166,9 +1166,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,19 +1193,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122234448</v>
+        <v>122234993</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1235,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563179</v>
+        <v>563147</v>
       </c>
       <c r="R7" t="n">
-        <v>7040282</v>
+        <v>7040405</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1268,19 +1278,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234993</v>
+        <v>122235058</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234448</v>
+        <v>122234993</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563179</v>
+        <v>563147</v>
       </c>
       <c r="R5" t="n">
-        <v>7040282</v>
+        <v>7040405</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,19 +1054,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122235369</v>
+        <v>122235058</v>
       </c>
       <c r="B6" t="n">
-        <v>90835</v>
+        <v>74757</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563130</v>
+        <v>563147</v>
       </c>
       <c r="R6" t="n">
-        <v>7040389</v>
+        <v>7040405</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1166,19 +1156,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,19 +1173,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122234993</v>
+        <v>122234448</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1245,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563147</v>
+        <v>563179</v>
       </c>
       <c r="R7" t="n">
-        <v>7040405</v>
+        <v>7040282</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1278,9 +1258,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,22 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122235058</v>
+        <v>122235369</v>
       </c>
       <c r="B8" t="n">
-        <v>74757</v>
+        <v>90835</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,13 +1337,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563147</v>
+        <v>563130</v>
       </c>
       <c r="R8" t="n">
-        <v>7040405</v>
+        <v>7040389</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,9 +1370,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,12 +1397,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234993</v>
+        <v>122235369</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>90829</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563147</v>
+        <v>563130</v>
       </c>
       <c r="R5" t="n">
-        <v>7040405</v>
+        <v>7040389</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,9 +1054,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122235058</v>
+        <v>122234448</v>
       </c>
       <c r="B6" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1133,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563147</v>
+        <v>563179</v>
       </c>
       <c r="R6" t="n">
-        <v>7040405</v>
+        <v>7040282</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,9 +1166,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,22 +1193,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122234448</v>
+        <v>122235058</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563179</v>
+        <v>563147</v>
       </c>
       <c r="R7" t="n">
-        <v>7040282</v>
+        <v>7040405</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,19 +1278,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122235369</v>
+        <v>122234993</v>
       </c>
       <c r="B8" t="n">
-        <v>90835</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,13 +1347,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563130</v>
+        <v>563147</v>
       </c>
       <c r="R8" t="n">
-        <v>7040389</v>
+        <v>7040405</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1370,19 +1380,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,12 +1397,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122234448</v>
+        <v>122235058</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,13 +1133,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563179</v>
+        <v>563147</v>
       </c>
       <c r="R6" t="n">
-        <v>7040282</v>
+        <v>7040405</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1166,19 +1166,9 @@
           <t>2025-01-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122235058</v>
+        <v>122234993</v>
       </c>
       <c r="B7" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1307,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234993</v>
+        <v>122234448</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1347,13 +1337,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563147</v>
+        <v>563179</v>
       </c>
       <c r="R8" t="n">
-        <v>7040405</v>
+        <v>7040282</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,9 +1370,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,12 +1397,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111630876</v>
+        <v>111630880</v>
       </c>
       <c r="B2" t="n">
-        <v>89745</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +710,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563341</v>
+        <v>563342</v>
       </c>
       <c r="R2" t="n">
         <v>7040192</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111630880</v>
+        <v>122235369</v>
       </c>
       <c r="B3" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Håsjön, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563341</v>
+        <v>563130</v>
       </c>
       <c r="R3" t="n">
-        <v>7040192</v>
+        <v>7040389</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,12 +882,7 @@
         <v>111630878</v>
       </c>
       <c r="B4" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,7 +914,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563341</v>
+        <v>563342</v>
       </c>
       <c r="R4" t="n">
         <v>7040192</v>
@@ -981,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122235369</v>
+        <v>111630874</v>
       </c>
       <c r="B5" t="n">
-        <v>90829</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563130</v>
+        <v>563366</v>
       </c>
       <c r="R5" t="n">
-        <v>7040389</v>
+        <v>7040276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,27 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122235058</v>
+        <v>122234359</v>
       </c>
       <c r="B6" t="n">
-        <v>74757</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,13 +1108,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563147</v>
+        <v>563205</v>
       </c>
       <c r="R6" t="n">
-        <v>7040405</v>
+        <v>7040240</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1166,9 +1141,19 @@
           <t>2025-01-20</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,65 +1168,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122234993</v>
+        <v>111630876</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563147</v>
+        <v>563342</v>
       </c>
       <c r="R7" t="n">
-        <v>7040405</v>
+        <v>7040192</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1265,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,31 +1265,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234448</v>
+        <v>122233217</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1333,14 +1308,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563179</v>
+        <v>562922</v>
       </c>
       <c r="R8" t="n">
-        <v>7040282</v>
+        <v>7040240</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,7 +1347,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1382,7 +1357,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1406,6 +1381,979 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122234194</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>563154</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7040221</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122234448</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>563179</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7040282</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122234993</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>563147</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7040405</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122235058</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>563147</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7040405</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122356076</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>563071</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7040224</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122233345</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>562904</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7040280</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122233647</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>562988</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7040196</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122234176</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>563102</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7040234</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122234283</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>563202</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7040231</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61323-2024 artfynd.xlsx
+++ b/artfynd/A 61323-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630880</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122235369</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630878</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630874</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234359</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630876</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233217</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234194</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1595,6 +1640,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234448</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234993</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122235058</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122356076</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2003,6 +2068,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233345</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2120,6 +2190,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122233647</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2237,6 +2312,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234176</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2354,8 +2434,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234283</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>